--- a/04_DESIGN_TABLES/DesignTable_2405_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2405_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ29"/>
+  <dimension ref="A1:AJ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2386,38 +2386,38 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2405-10-08</t>
+          <t>2405-10-06</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="C16" t="n">
-        <v>0.65241</v>
+        <v>0.54155</v>
       </c>
       <c r="D16" t="n">
-        <v>1.13</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9</v>
+        <v>0.68</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9</v>
+        <v>0.68</v>
       </c>
       <c r="I16" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="J16" t="n">
-        <v>0.35</v>
+        <v>0.285</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4071</v>
+        <v>0.3294</v>
       </c>
       <c r="L16" t="n">
         <v>0.4375</v>
@@ -2462,19 +2462,19 @@
         <v>0.07142999999999999</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.48</v>
+        <v>0.484</v>
       </c>
       <c r="AA16" t="n">
         <v>0.99</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2405-10-08</t>
+          <t>2405-10-06</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Female Connector, 7/8-14 JIC x 1/2-14 NPTF (female)</t>
+          <t>Female Connector, 7/8-14 JIC x 3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2494,60 +2494,60 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>JIC end: MS33656J==Brennan (VERIFIED); female NPTF: AW tap drill + MS51503 P1 max; L2/hex: Air-Way==MS51503 | MODEL: female NPTF port (End A): Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs confirm P1 = the port drill depth), tapered helical thread over P1; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L2 / hex: review table (Air-Way; matched rows == MS51503D); hex from the port face to the JIC end (legacy 2405 builder); through bore D3 (Air-Way) from the JIC tip to the port bottom; hex end chamfers and the port countersink NOT modelled</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L2@DRIVE: Brennan TFA catalog p7 table TFA-p007-t02 "2405 MJ-FP STRAIGHT" row 2405-10-06 col "L LGTH" = "1.670" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 506.2, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p7 2405 drawing: L = overall, C HEX = body hex, B1 DRILL = through bore from the JIC end (impact/F2a.json, certain); same-table check on today's base: 28/32 rows with an Air-Way/OMi value agree with this catalog column to rounding (4 differ, e.g. 2405-03-04 1.32 vs 1.31); HEXB@HEX: Brennan TFA catalog p7 table TFA-p007-t02 "2405 MJ-FP STRAIGHT" row 2405-10-06 col "C HEX" = "0.938" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 506.2, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p7 2405 drawing: L = overall, C HEX = body hex, B1 DRILL = through bore from the JIC end (impact/F2a.json, certain); same-table check on today's base: 32/32 rows with an Air-Way/OMi value agree with this catalog column to rounding; D3@BORE_THRU: Brennan TFA catalog p7 table TFA-p007-t02 "2405 MJ-FP STRAIGHT" row 2405-10-06 col "B1 DRILL" = "0.484" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 506.2, page verified) [Brennan = yes 2026-10-18] - through bore from the JIC end; mapping: TFA p7 2405 drawing: L = overall, C HEX = body hex, B1 DRILL = through bore from the JIC end (impact/F2a.json, certain); same-table check on today's base: 32/32 rows with an Air-Way/OMi value agree with this catalog column to rounding; THDMAJ_B@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; JIC_RELIEFL@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] RL (end detail per dash); JIC_THDZ@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] TZ (end detail per dash); JIC_CONEDIA@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] CD (end detail per dash); JIC_LANDL@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] LL (end detail per dash); JIC_SEATL@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] SL (end detail per dash); RELIEFANG@DRIVE: gen_straight2 end_JICM constant 60 deg relief ramp (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; SEATB@DRIVE: gen_straight2 end_JICM constant 37 deg flare seat (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; FPT_P1@DRIVE: end library gen_straight2 FPT[6] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.57, FPT_P1 0.68 = MS51503 P1 max) - port depth = MS51503 P1 max per pipe dash (end detail) [Q-TRANSFER-ENDLIB yes]; TAPDRILL@BORE_A: end library gen_straight2 FPT[6] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.57, FPT_P1 0.68 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; $PRP@EndA_Thread: end library gen_straight2 FPT[6] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.57, FPT_P1 0.68 = MS51503 P1 max) thread text; $PRP@EndB_Thread: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread text | MODEL: female NPTF port (End A): Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs confirm P1 = the port drill depth), tapered helical thread over P1; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L2 / hex: review table (Air-Way; matched rows == MS51503D); hex from the port face to the JIC end (legacy 2405 builder); through bore D3 (Air-Way) from the JIC tip to the port bottom; hex end chamfers and the port countersink NOT modelled</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>MS51503D Amd1 L2/hex AGREE</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L2 / hex / D3 from the Brennan TFA catalog p7 alone; JIC end + port depth from the end library; tap drill = Air-Way per size (A1 yes)</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2405-10-08</t>
+          <t>2405-10-06</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2405-10-12</t>
+          <t>2405-10-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="C17" t="n">
-        <v>0.79674</v>
+        <v>0.65241</v>
       </c>
       <c r="D17" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="E17" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="F17" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="G17" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="H17" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="I17" t="n">
         <v>0.07140000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.455</v>
+        <v>0.35</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5121</v>
+        <v>0.4071</v>
       </c>
       <c r="L17" t="n">
         <v>0.4375</v>
@@ -2595,16 +2595,16 @@
         <v>0.48</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.04</v>
+        <v>0.99</v>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2405-10-12</t>
+          <t>2405-10-08</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Female Connector, 7/8-14 JIC x 3/4-14 NPTF (female)</t>
+          <t>Female Connector, 7/8-14 JIC x 1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2624,73 +2624,78 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>JIC end: MS33656J==Brennan (VERIFIED); female NPTF: AW tap drill + MS51503 P1 max; L2/hex: Air-Way | MODEL: female NPTF port (End A): Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs confirm P1 = the port drill depth), tapered helical thread over P1; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L2 / hex: review table (Air-Way; matched rows == MS51503D); hex from the port face to the JIC end (legacy 2405 builder); through bore D3 (Air-Way) from the JIC tip to the port bottom; hex end chamfers and the port countersink NOT modelled</t>
+          <t>JIC end: MS33656J==Brennan (VERIFIED); female NPTF: AW tap drill + MS51503 P1 max; L2/hex: Air-Way==MS51503 | MODEL: female NPTF port (End A): Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs confirm P1 = the port drill depth), tapered helical thread over P1; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L2 / hex: review table (Air-Way; matched rows == MS51503D); hex from the port face to the JIC end (legacy 2405 builder); through bore D3 (Air-Way) from the JIC tip to the port bottom; hex end chamfers and the port countersink NOT modelled</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>MS51503D Amd1 L2/hex AGREE</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2405-10-12</t>
+          <t>2405-10-08</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2405-12-08</t>
+          <t>2405-10-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="C18" t="n">
-        <v>0.65241</v>
+        <v>0.79674</v>
       </c>
       <c r="D18" t="n">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="I18" t="n">
         <v>0.07140000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.35</v>
+        <v>0.455</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4071</v>
+        <v>0.5121</v>
       </c>
       <c r="L18" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="M18" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3895</v>
+        <v>0.3553</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4715</v>
+        <v>0.386</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1299</v>
+        <v>0.1114</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="R18" t="n">
         <v>60</v>
@@ -2699,37 +2704,37 @@
         <v>37</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="U18" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7045</v>
+        <v>0.6213</v>
       </c>
       <c r="W18" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="X18" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2405-12-08</t>
+          <t>2405-10-12</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Female Connector, 1 1/16-12 JIC x 1/2-14 NPTF (female)</t>
+          <t>Female Connector, 7/8-14 JIC x 3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -2739,12 +2744,12 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF (female)</t>
+          <t>3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>1 1/16-12</t>
+          <t>7/8-14</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -2759,45 +2764,45 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2405-12-08</t>
+          <t>2405-10-12</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2405-12-12</t>
+          <t>2405-12-08</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="C19" t="n">
-        <v>0.79674</v>
+        <v>0.65241</v>
       </c>
       <c r="D19" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="E19" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="F19" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="G19" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="H19" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="I19" t="n">
         <v>0.07140000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.455</v>
+        <v>0.35</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5121</v>
+        <v>0.4071</v>
       </c>
       <c r="L19" t="n">
         <v>0.53125</v>
@@ -2849,12 +2854,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2405-12-12</t>
+          <t>2405-12-08</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Female Connector, 1 1/16-12 JIC x 3/4-14 NPTF (female)</t>
+          <t>Female Connector, 1 1/16-12 JIC x 1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -2864,7 +2869,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2874,60 +2879,55 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>JIC end: MS33656J==Brennan (VERIFIED); female NPTF: AW tap drill + MS51503 P1 max; L2/hex: Air-Way==MS51503 | MODEL: female NPTF port (End A): Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs confirm P1 = the port drill depth), tapered helical thread over P1; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L2 / hex: review table (Air-Way; matched rows == MS51503D); hex from the port face to the JIC end (legacy 2405 builder); through bore D3 (Air-Way) from the JIC tip to the port bottom; hex end chamfers and the port countersink NOT modelled</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>MS51503D Amd1 L2/hex AGREE</t>
+          <t>JIC end: MS33656J==Brennan (VERIFIED); female NPTF: AW tap drill + MS51503 P1 max; L2/hex: Air-Way | MODEL: female NPTF port (End A): Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs confirm P1 = the port drill depth), tapered helical thread over P1; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L2 / hex: review table (Air-Way; matched rows == MS51503D); hex from the port face to the JIC end (legacy 2405 builder); through bore D3 (Air-Way) from the JIC tip to the port bottom; hex end chamfers and the port countersink NOT modelled</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2405-12-12</t>
+          <t>2405-12-08</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2405-12-16</t>
+          <t>2405-12-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="C20" t="n">
-        <v>0.94108</v>
+        <v>0.79674</v>
       </c>
       <c r="D20" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="E20" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="F20" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="G20" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="H20" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="I20" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.57</v>
+        <v>0.455</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.5121</v>
       </c>
       <c r="L20" t="n">
         <v>0.53125</v>
@@ -2975,16 +2975,16 @@
         <v>0.61</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2405-12-16</t>
+          <t>2405-12-12</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Female Connector, 1 1/16-12 JIC x 1-11 1/2 NPTF (female)</t>
+          <t>Female Connector, 1 1/16-12 JIC x 3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF (female)</t>
+          <t>3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -3004,73 +3004,78 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>JIC end: MS33656J==Brennan (VERIFIED); female NPTF: AW tap drill + MS51503 P1 max; L2/hex: Air-Way | MODEL: female NPTF port (End A): Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs confirm P1 = the port drill depth), tapered helical thread over P1; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L2 / hex: review table (Air-Way; matched rows == MS51503D); hex from the port face to the JIC end (legacy 2405 builder); through bore D3 (Air-Way) from the JIC tip to the port bottom; hex end chamfers and the port countersink NOT modelled</t>
+          <t>JIC end: MS33656J==Brennan (VERIFIED); female NPTF: AW tap drill + MS51503 P1 max; L2/hex: Air-Way==MS51503 | MODEL: female NPTF port (End A): Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs confirm P1 = the port drill depth), tapered helical thread over P1; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L2 / hex: review table (Air-Way; matched rows == MS51503D); hex from the port face to the JIC end (legacy 2405 builder); through bore D3 (Air-Way) from the JIC tip to the port bottom; hex end chamfers and the port countersink NOT modelled</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>MS51503D Amd1 L2/hex AGREE</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2405-12-16</t>
+          <t>2405-12-12</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2405-16-12</t>
+          <t>2405-12-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="C21" t="n">
-        <v>0.79674</v>
+        <v>0.94108</v>
       </c>
       <c r="D21" t="n">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="E21" t="n">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="F21" t="n">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="G21" t="n">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="H21" t="n">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="I21" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0.455</v>
+        <v>0.57</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5121</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="M21" t="n">
         <v>0.125</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5965</v>
+        <v>0.4715</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="R21" t="n">
         <v>60</v>
@@ -3079,13 +3084,13 @@
         <v>37</v>
       </c>
       <c r="T21" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="U21" t="n">
         <v>0.08333</v>
       </c>
       <c r="V21" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7045</v>
       </c>
       <c r="W21" t="n">
         <v>0.04511</v>
@@ -3097,19 +3102,19 @@
         <v>0.08333</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2405-16-12</t>
+          <t>2405-12-16</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Female Connector, 1 5/16-12 JIC x 3/4-14 NPTF (female)</t>
+          <t>Female Connector, 1 1/16-12 JIC x 1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -3119,12 +3124,12 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>1 5/16-12</t>
+          <t>1 1/16-12</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -3139,57 +3144,57 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2405-16-12</t>
+          <t>2405-12-16</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2405-16-16</t>
+          <t>2405-14-12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="C22" t="n">
-        <v>0.94108</v>
+        <v>0.79386</v>
       </c>
       <c r="D22" t="n">
-        <v>1.63</v>
+        <v>1.375</v>
       </c>
       <c r="E22" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="F22" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="G22" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="H22" t="n">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="I22" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.57</v>
+        <v>0.455</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.5121</v>
       </c>
       <c r="L22" t="n">
-        <v>0.65625</v>
+        <v>0.59375</v>
       </c>
       <c r="M22" t="n">
         <v>0.125</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4365</v>
+        <v>0.4155</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5965</v>
+        <v>0.534</v>
       </c>
       <c r="P22" t="n">
         <v>0.1292</v>
@@ -3204,13 +3209,13 @@
         <v>37</v>
       </c>
       <c r="T22" t="n">
-        <v>1.3125</v>
+        <v>1.1875</v>
       </c>
       <c r="U22" t="n">
         <v>0.08333</v>
       </c>
       <c r="V22" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7305</v>
       </c>
       <c r="W22" t="n">
         <v>0.04511</v>
@@ -3222,19 +3227,19 @@
         <v>0.08333</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.84</v>
+        <v>0.719</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2405-16-16</t>
+          <t>2405-14-12</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Female Connector, 1 5/16-12 JIC x 1-11 1/2 NPTF (female)</t>
+          <t>Female Connector, 1 3/16-12 JIC x 3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -3244,70 +3249,70 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF (female)</t>
+          <t>3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>1 5/16-12</t>
+          <t>1 3/16-12</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>JIC end: MS33656J==Brennan (VERIFIED); female NPTF: AW tap drill + MS51503 P1 max; L2/hex: Air-Way==MS51503 | MODEL: female NPTF port (End A): Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs confirm P1 = the port drill depth), tapered helical thread over P1; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L2 / hex: review table (Air-Way; matched rows == MS51503D); hex from the port face to the JIC end (legacy 2405 builder); through bore D3 (Air-Way) from the JIC tip to the port bottom; hex end chamfers and the port countersink NOT modelled</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L2@DRIVE: Brennan TFA catalog p7 table TFA-p007-t02 "2405 MJ-FP STRAIGHT" row 2405-14-12 col "L LGTH" = "2.06" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 586.9, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p7 2405 drawing: L = overall, C HEX = body hex, B1 DRILL = through bore from the JIC end (impact/F2a.json, certain); same-table check on today's base: 28/32 rows with an Air-Way/OMi value agree with this catalog column to rounding (4 differ, e.g. 2405-03-04 1.32 vs 1.31); HEXB@HEX: Brennan TFA catalog p7 table TFA-p007-t02 "2405 MJ-FP STRAIGHT" row 2405-14-12 col "C HEX" = "1.375" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 586.9, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p7 2405 drawing: L = overall, C HEX = body hex, B1 DRILL = through bore from the JIC end (impact/F2a.json, certain); same-table check on today's base: 32/32 rows with an Air-Way/OMi value agree with this catalog column to rounding; D3@BORE_THRU: Brennan TFA catalog p7 table TFA-p007-t02 "2405 MJ-FP STRAIGHT" row 2405-14-12 col "B1 DRILL" = "0.719" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 586.9, page verified) [Brennan = yes 2026-10-18] - through bore from the JIC end; mapping: TFA p7 2405 drawing: L = overall, C HEX = body hex, B1 DRILL = through bore from the JIC end (impact/F2a.json, certain); same-table check on today's base: 32/32 rows with an Air-Way/OMi value agree with this catalog column to rounding; THDMAJ_B@DRIVE: end library gen_straight2 JIC[14] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; JIC_RELIEFL@DRIVE: end library gen_straight2 JIC[14] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] RL (end detail per dash); JIC_THDZ@DRIVE: end library gen_straight2 JIC[14] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] TZ (end detail per dash); JIC_CONEDIA@DRIVE: end library gen_straight2 JIC[14] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] CD (end detail per dash); JIC_LANDL@DRIVE: end library gen_straight2 JIC[14] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] LL (end detail per dash); JIC_SEATL@DRIVE: end library gen_straight2 JIC[14] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] SL (end detail per dash); RELIEFANG@DRIVE: gen_straight2 end_JICM constant 60 deg relief ramp (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; SEATB@DRIVE: gen_straight2 end_JICM constant 37 deg flare seat (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; FPT_P1@DRIVE: end library gen_straight2 FPT[12] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.91, FPT_P1 0.91 = MS51503 P1 max) - port depth = MS51503 P1 max per pipe dash (end detail) [Q-TRANSFER-ENDLIB yes]; TAPDRILL@BORE_A: end library gen_straight2 FPT[12] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.91, FPT_P1 0.91 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; $PRP@EndA_Thread: end library gen_straight2 FPT[12] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.91, FPT_P1 0.91 = MS51503 P1 max) thread text; $PRP@EndB_Thread: end library gen_straight2 JIC[14] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread text | MODEL: female NPTF port (End A): Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs confirm P1 = the port drill depth), tapered helical thread over P1; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L2 / hex: review table (Air-Way; matched rows == MS51503D); hex from the port face to the JIC end (legacy 2405 builder); through bore D3 (Air-Way) from the JIC tip to the port bottom; hex end chamfers and the port countersink NOT modelled</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>MS51503D Amd1 L2/hex AGREE</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L2 / hex / D3 from the Brennan TFA catalog p7 alone; JIC end + port depth from the end library; tap drill = Air-Way per size (A1 yes)</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2405-16-16</t>
+          <t>2405-14-12</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2405-16-20</t>
+          <t>2405-16-12</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.44</v>
+        <v>2.12</v>
       </c>
       <c r="C23" t="n">
-        <v>1.1547</v>
+        <v>0.79674</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="E23" t="n">
-        <v>1.48</v>
+        <v>0.91</v>
       </c>
       <c r="F23" t="n">
-        <v>1.16</v>
+        <v>0.91</v>
       </c>
       <c r="G23" t="n">
-        <v>1.48</v>
+        <v>0.91</v>
       </c>
       <c r="H23" t="n">
-        <v>1.16</v>
+        <v>0.91</v>
       </c>
       <c r="I23" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>0.74</v>
+        <v>0.455</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8096</v>
+        <v>0.5121</v>
       </c>
       <c r="L23" t="n">
         <v>0.65625</v>
@@ -3355,16 +3360,16 @@
         <v>0.84</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2405-16-20</t>
+          <t>2405-16-12</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Female Connector, 1 5/16-12 JIC x 1 1/4-11 1/2 NPTF (female)</t>
+          <t>Female Connector, 1 5/16-12 JIC x 3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -3374,7 +3379,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF (female)</t>
+          <t>3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3394,24 +3399,24 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2405-16-20</t>
+          <t>2405-16-12</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2405-20-16</t>
+          <t>2405-16-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="C24" t="n">
-        <v>0.97572</v>
+        <v>0.94108</v>
       </c>
       <c r="D24" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="E24" t="n">
         <v>1.14</v>
@@ -3435,22 +3440,22 @@
         <v>0.6395999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="M24" t="n">
         <v>0.125</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="O24" t="n">
-        <v>0.753</v>
+        <v>0.5965</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="R24" t="n">
         <v>60</v>
@@ -3459,13 +3464,13 @@
         <v>37</v>
       </c>
       <c r="T24" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="U24" t="n">
         <v>0.08333</v>
       </c>
       <c r="V24" t="n">
-        <v>0.7986</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="W24" t="n">
         <v>0.04511</v>
@@ -3477,19 +3482,19 @@
         <v>0.08333</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2405-20-16</t>
+          <t>2405-16-16</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Female Connector, 1 5/8-12 JIC x 1-11 1/2 NPTF (female)</t>
+          <t>Female Connector, 1 5/16-12 JIC x 1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -3504,33 +3509,38 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>1 5/8-12</t>
+          <t>1 5/16-12</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>JIC end: MS33656J==Brennan (VERIFIED); female NPTF: AW tap drill + MS51503 P1 max; L2/hex: Air-Way | MODEL: female NPTF port (End A): Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs confirm P1 = the port drill depth), tapered helical thread over P1; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L2 / hex: review table (Air-Way; matched rows == MS51503D); hex from the port face to the JIC end (legacy 2405 builder); through bore D3 (Air-Way) from the JIC tip to the port bottom; hex end chamfers and the port countersink NOT modelled</t>
+          <t>JIC end: MS33656J==Brennan (VERIFIED); female NPTF: AW tap drill + MS51503 P1 max; L2/hex: Air-Way==MS51503 | MODEL: female NPTF port (End A): Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs confirm P1 = the port drill depth), tapered helical thread over P1; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L2 / hex: review table (Air-Way; matched rows == MS51503D); hex from the port face to the JIC end (legacy 2405 builder); through bore D3 (Air-Way) from the JIC tip to the port bottom; hex end chamfers and the port countersink NOT modelled</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>MS51503D Amd1 L2/hex AGREE</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>2405-20-16</t>
+          <t>2405-16-16</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2405-20-20</t>
+          <t>2405-16-20</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="C25" t="n">
         <v>1.1547</v>
@@ -3560,22 +3570,22 @@
         <v>0.8096</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="M25" t="n">
         <v>0.125</v>
       </c>
       <c r="N25" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="O25" t="n">
-        <v>0.753</v>
+        <v>0.5965</v>
       </c>
       <c r="P25" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="R25" t="n">
         <v>60</v>
@@ -3584,13 +3594,13 @@
         <v>37</v>
       </c>
       <c r="T25" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="U25" t="n">
         <v>0.08333</v>
       </c>
       <c r="V25" t="n">
-        <v>0.7986</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="W25" t="n">
         <v>0.04511</v>
@@ -3602,19 +3612,19 @@
         <v>0.08333</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2405-20-20</t>
+          <t>2405-16-20</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Female Connector, 1 5/8-12 JIC x 1 1/4-11 1/2 NPTF (female)</t>
+          <t>Female Connector, 1 5/16-12 JIC x 1 1/4-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -3629,65 +3639,60 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>1 5/8-12</t>
+          <t>1 5/16-12</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>JIC end: MS33656J==Brennan (VERIFIED); female NPTF: AW tap drill + MS51503 P1 max; L2/hex: Air-Way==MS51503 | MODEL: female NPTF port (End A): Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs confirm P1 = the port drill depth), tapered helical thread over P1; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L2 / hex: review table (Air-Way; matched rows == MS51503D); hex from the port face to the JIC end (legacy 2405 builder); through bore D3 (Air-Way) from the JIC tip to the port bottom; hex end chamfers and the port countersink NOT modelled</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>MS51503D Amd1 L2/hex AGREE</t>
+          <t>JIC end: MS33656J==Brennan (VERIFIED); female NPTF: AW tap drill + MS51503 P1 max; L2/hex: Air-Way | MODEL: female NPTF port (End A): Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs confirm P1 = the port drill depth), tapered helical thread over P1; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L2 / hex: review table (Air-Way; matched rows == MS51503D); hex from the port face to the JIC end (legacy 2405 builder); through bore D3 (Air-Way) from the JIC tip to the port bottom; hex end chamfers and the port countersink NOT modelled</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>2405-20-20</t>
+          <t>2405-16-20</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2405-20-24</t>
+          <t>2405-20-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="C26" t="n">
-        <v>1.37409</v>
+        <v>0.97572</v>
       </c>
       <c r="D26" t="n">
-        <v>2.38</v>
+        <v>1.69</v>
       </c>
       <c r="E26" t="n">
-        <v>1.72</v>
+        <v>1.14</v>
       </c>
       <c r="F26" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="G26" t="n">
-        <v>1.72</v>
+        <v>1.14</v>
       </c>
       <c r="H26" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="I26" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>0.86</v>
+        <v>0.57</v>
       </c>
       <c r="K26" t="n">
-        <v>0.9296</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="L26" t="n">
         <v>0.8125</v>
@@ -3739,12 +3744,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2405-20-24</t>
+          <t>2405-20-16</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Female Connector, 1 5/8-12 JIC x 1 1/2-11 1/2 NPTF (female)</t>
+          <t>Female Connector, 1 5/8-12 JIC x 1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -3754,7 +3759,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF (female)</t>
+          <t>1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3774,33 +3779,33 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>2405-20-24</t>
+          <t>2405-20-16</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2405-24-24</t>
+          <t>2405-20-20</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="C27" t="n">
-        <v>1.37409</v>
+        <v>1.1547</v>
       </c>
       <c r="D27" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="F27" t="n">
         <v>1.16</v>
       </c>
       <c r="G27" t="n">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="H27" t="n">
         <v>1.16</v>
@@ -3809,28 +3814,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>0.86</v>
+        <v>0.74</v>
       </c>
       <c r="K27" t="n">
-        <v>0.9296</v>
+        <v>0.8096</v>
       </c>
       <c r="L27" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="M27" t="n">
         <v>0.125</v>
       </c>
       <c r="N27" t="n">
-        <v>0.5454</v>
+        <v>0.4316</v>
       </c>
       <c r="O27" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="P27" t="n">
-        <v>0.1298</v>
+        <v>0.1288</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.2482</v>
+        <v>0.2382</v>
       </c>
       <c r="R27" t="n">
         <v>60</v>
@@ -3839,13 +3844,13 @@
         <v>37</v>
       </c>
       <c r="T27" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="U27" t="n">
         <v>0.08333</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9234</v>
+        <v>0.7986</v>
       </c>
       <c r="W27" t="n">
         <v>0.04511</v>
@@ -3857,19 +3862,19 @@
         <v>0.08333</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2405-24-24</t>
+          <t>2405-20-20</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Female Connector, 1 7/8-12 JIC x 1 1/2-11 1/2 NPTF (female)</t>
+          <t>Female Connector, 1 5/8-12 JIC x 1 1/4-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -3879,12 +3884,12 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF (female)</t>
+          <t>1 1/4-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>1 7/8-12</t>
+          <t>1 5/8-12</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -3904,63 +3909,63 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>2405-24-24</t>
+          <t>2405-20-20</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2405-24-32</t>
+          <t>2405-20-24</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.73</v>
+        <v>2.49</v>
       </c>
       <c r="C28" t="n">
-        <v>1.66277</v>
+        <v>1.37409</v>
       </c>
       <c r="D28" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="E28" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="F28" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="G28" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="H28" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="I28" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>1.1</v>
+        <v>0.86</v>
       </c>
       <c r="K28" t="n">
-        <v>1.1696</v>
+        <v>0.9296</v>
       </c>
       <c r="L28" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="M28" t="n">
         <v>0.125</v>
       </c>
       <c r="N28" t="n">
-        <v>0.5454</v>
+        <v>0.4316</v>
       </c>
       <c r="O28" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="P28" t="n">
-        <v>0.1298</v>
+        <v>0.1288</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.2482</v>
+        <v>0.2382</v>
       </c>
       <c r="R28" t="n">
         <v>60</v>
@@ -3969,13 +3974,13 @@
         <v>37</v>
       </c>
       <c r="T28" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="U28" t="n">
         <v>0.08333</v>
       </c>
       <c r="V28" t="n">
-        <v>0.9234</v>
+        <v>0.7986</v>
       </c>
       <c r="W28" t="n">
         <v>0.04511</v>
@@ -3987,19 +3992,19 @@
         <v>0.08333</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2405-24-32</t>
+          <t>2405-20-24</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Female Connector, 1 7/8-12 JIC x 2-11 1/2 NPTF (female)</t>
+          <t>Female Connector, 1 5/8-12 JIC x 1 1/2-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -4009,12 +4014,12 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2-11 1/2 NPTF (female)</t>
+          <t>1 1/2-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>1 7/8-12</t>
+          <t>1 5/8-12</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -4029,63 +4034,63 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>2405-24-32</t>
+          <t>2405-20-24</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2405-32-32</t>
+          <t>2405-24-24</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.97</v>
+        <v>2.62</v>
       </c>
       <c r="C29" t="n">
-        <v>1.66277</v>
+        <v>1.37409</v>
       </c>
       <c r="D29" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="E29" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="F29" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="G29" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="H29" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="I29" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>1.1</v>
+        <v>0.86</v>
       </c>
       <c r="K29" t="n">
-        <v>1.1696</v>
+        <v>0.9296</v>
       </c>
       <c r="L29" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="M29" t="n">
         <v>0.125</v>
       </c>
       <c r="N29" t="n">
-        <v>0.7124</v>
+        <v>0.5454</v>
       </c>
       <c r="O29" t="n">
-        <v>1.19</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="P29" t="n">
-        <v>0.1292</v>
+        <v>0.1298</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.3318</v>
+        <v>0.2482</v>
       </c>
       <c r="R29" t="n">
         <v>60</v>
@@ -4094,13 +4099,13 @@
         <v>37</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>1.875</v>
       </c>
       <c r="U29" t="n">
         <v>0.08333</v>
       </c>
       <c r="V29" t="n">
-        <v>1.1734</v>
+        <v>0.9234</v>
       </c>
       <c r="W29" t="n">
         <v>0.04511</v>
@@ -4112,52 +4117,307 @@
         <v>0.08333</v>
       </c>
       <c r="Z29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>2405-24-24</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Female Connector, 1 7/8-12 JIC x 1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>2405</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>1 7/8-12</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>JIC end: MS33656J==Brennan (VERIFIED); female NPTF: AW tap drill + MS51503 P1 max; L2/hex: Air-Way==MS51503 | MODEL: female NPTF port (End A): Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs confirm P1 = the port drill depth), tapered helical thread over P1; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L2 / hex: review table (Air-Way; matched rows == MS51503D); hex from the port face to the JIC end (legacy 2405 builder); through bore D3 (Air-Way) from the JIC tip to the port bottom; hex end chamfers and the port countersink NOT modelled</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>MS51503D Amd1 L2/hex AGREE</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>2405-24-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2405-24-32</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.66277</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.1696</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.8774999999999999</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="R30" t="n">
+        <v>60</v>
+      </c>
+      <c r="S30" t="n">
+        <v>37</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.9234</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>2405-24-32</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Female Connector, 1 7/8-12 JIC x 2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>2405</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>1 7/8-12</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>JIC end: MS33656J==Brennan (VERIFIED); female NPTF: AW tap drill + MS51503 P1 max; L2/hex: Air-Way | MODEL: female NPTF port (End A): Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs confirm P1 = the port drill depth), tapered helical thread over P1; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L2 / hex: review table (Air-Way; matched rows == MS51503D); hex from the port face to the JIC end (legacy 2405 builder); through bore D3 (Air-Way) from the JIC tip to the port bottom; hex end chamfers and the port countersink NOT modelled</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>2405-24-32</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2405-32-32</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.66277</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.1696</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="R31" t="n">
+        <v>60</v>
+      </c>
+      <c r="S31" t="n">
+        <v>37</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.1734</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Z31" t="n">
         <v>1.78</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AA31" t="n">
         <v>1.79</v>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>2405-32-32</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>Female Connector, 2 1/2-12 JIC x 2-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>2405</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr">
+      <c r="AE31" t="inlineStr">
         <is>
           <t>2-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="AF29" t="inlineStr">
+      <c r="AF31" t="inlineStr">
         <is>
           <t>2 1/2-12</t>
         </is>
       </c>
-      <c r="AG29" t="inlineStr">
+      <c r="AG31" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
       </c>
-      <c r="AH29" t="inlineStr">
+      <c r="AH31" t="inlineStr">
         <is>
           <t>JIC end: MS33656J==Brennan (VERIFIED); female NPTF: AW tap drill + MS51503 P1 max; L2/hex: Air-Way==MS51503 | MODEL: female NPTF port (End A): Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405 STEPs confirm P1 = the port drill depth), tapered helical thread over P1; JIC end (End B): MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L2 / hex: review table (Air-Way; matched rows == MS51503D); hex from the port face to the JIC end (legacy 2405 builder); through bore D3 (Air-Way) from the JIC tip to the port bottom; hex end chamfers and the port countersink NOT modelled</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
+      <c r="AI31" t="inlineStr">
         <is>
           <t>MS51503D Amd1 L2/hex AGREE</t>
         </is>
       </c>
-      <c r="AJ29" t="inlineStr">
+      <c r="AJ31" t="inlineStr">
         <is>
           <t>2405-32-32</t>
         </is>
